--- a/result.xlsx
+++ b/result.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="213">
-  <si>
-    <t>SJSU vs UCD vs UCSC</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="183">
+  <si>
+    <t>STANFORD vs UCD vs UCSC</t>
   </si>
   <si>
     <t>Instructions:
@@ -55,601 +55,511 @@
     <t>Winner Flags (M=Team1, N=Team2)</t>
   </si>
   <si>
-    <t>10:15</t>
+    <t>12:10</t>
   </si>
   <si>
     <t>WD1</t>
   </si>
   <si>
+    <t>UCSC</t>
+  </si>
+  <si>
+    <t>STANFORD</t>
+  </si>
+  <si>
+    <t>Jenny Lei + Sydney Stachovic</t>
+  </si>
+  <si>
+    <t>Amanda Ng + Rachel Ye</t>
+  </si>
+  <si>
+    <t>XD8</t>
+  </si>
+  <si>
+    <t>Jiaying Zhang + Hao Yuan Zhu</t>
+  </si>
+  <si>
+    <t>Max Xing + Helena Xu</t>
+  </si>
+  <si>
+    <t>XD4</t>
+  </si>
+  <si>
+    <t>Erin Chang + Alex Davis</t>
+  </si>
+  <si>
+    <t>Nachiketh Karthik + Alexa Tyberg</t>
+  </si>
+  <si>
+    <t>WD3</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>SJSU</t>
-  </si>
-  <si>
-    <t>Xin Huang + Rithika Oumapathy</t>
-  </si>
-  <si>
-    <t>Sankhya Gunda + Amber Li</t>
-  </si>
-  <si>
-    <t>WD7</t>
-  </si>
-  <si>
-    <t>Livia Rice + Minh Nguyen</t>
-  </si>
-  <si>
-    <t>Shani Chiu + Rupashi Bahl</t>
+    <t>Gaby imholte + Carolyn Suryapermana</t>
+  </si>
+  <si>
+    <t>Veronica Chang + Jingyu Zhang</t>
+  </si>
+  <si>
+    <t>XD6</t>
+  </si>
+  <si>
+    <t>Ryan Lei + Jamie Yip</t>
+  </si>
+  <si>
+    <t>Melvin Keat + Christine Zhang</t>
+  </si>
+  <si>
+    <t>MD1</t>
+  </si>
+  <si>
+    <t>Sam Lai + Sashreek Rewatkar</t>
+  </si>
+  <si>
+    <t>Jerry Yuan + Nikil Selvam</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>MD2</t>
+  </si>
+  <si>
+    <t>Sam Lai + Jason Chen</t>
+  </si>
+  <si>
+    <t>MD5</t>
+  </si>
+  <si>
+    <t>Akhilesh Nidamanuri + Jayden Ma</t>
+  </si>
+  <si>
+    <t>Nachiketh Karthik + Max Xing</t>
+  </si>
+  <si>
+    <t>WD2</t>
+  </si>
+  <si>
+    <t>Livia Rice + Jamie Yip</t>
+  </si>
+  <si>
+    <t>Alexa Tyberg + Veronica Chang</t>
+  </si>
+  <si>
+    <t>XD5</t>
+  </si>
+  <si>
+    <t>Sydney Stachovic + Howell Zhang</t>
+  </si>
+  <si>
+    <t>Luke Shen + Jingyu Zhang</t>
+  </si>
+  <si>
+    <t>Jenna Nguyen + Rhea Rajan</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>XD2</t>
+  </si>
+  <si>
+    <t>Jenny Lei + Jayden Ma</t>
+  </si>
+  <si>
+    <t>Nikil Selvam + Amanda Ng</t>
+  </si>
+  <si>
+    <t>XD1</t>
+  </si>
+  <si>
+    <t>Rhea Rajan + Akhilesh Nidamanuri</t>
+  </si>
+  <si>
+    <t>Jerry Yuan + Rachel Ye</t>
+  </si>
+  <si>
+    <t>XD7</t>
+  </si>
+  <si>
+    <t>MD4</t>
+  </si>
+  <si>
+    <t>Alex Davis + Akshay Ganapathi</t>
+  </si>
+  <si>
+    <t>Luke Shen + Melvin Keat</t>
+  </si>
+  <si>
+    <t>Justin Larson + Livia Rice</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>Jon Moser + Sidney Wang</t>
+  </si>
+  <si>
+    <t>Jerry Qiu + Mariano</t>
+  </si>
+  <si>
+    <t>Rithika Oumapathy + Kristine Ngo</t>
+  </si>
+  <si>
+    <t>WS4</t>
+  </si>
+  <si>
+    <t>Carolyn Suryapermana</t>
+  </si>
+  <si>
+    <t>Jiaying Zhang</t>
+  </si>
+  <si>
+    <t>MD3</t>
+  </si>
+  <si>
+    <t>Harry Liu + Justin Chen</t>
+  </si>
+  <si>
+    <t>Nikil Selvam + Evan Chen</t>
+  </si>
+  <si>
+    <t>01:50</t>
   </si>
   <si>
     <t>WD4</t>
   </si>
   <si>
-    <t>Jasmeet Dhillon + Jamie Yip</t>
-  </si>
-  <si>
-    <t>Emily Kung + Natalie Luong</t>
+    <t>Helena Xu + Christine Zhang</t>
+  </si>
+  <si>
+    <t>WS5</t>
+  </si>
+  <si>
+    <t>Jingyu Zhang</t>
+  </si>
+  <si>
+    <t>Benson Ngai + Jonathan Li</t>
+  </si>
+  <si>
+    <t>Emily Lam + Jennifer Kim</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>Benson Ngai + Kristine Ngo</t>
+  </si>
+  <si>
+    <t>WS1</t>
+  </si>
+  <si>
+    <t>Erin Chang</t>
+  </si>
+  <si>
+    <t>Amanda Ng</t>
+  </si>
+  <si>
+    <t>Josh Luo + Emily Chen</t>
+  </si>
+  <si>
+    <t>Christine Zhang</t>
+  </si>
+  <si>
+    <t>XD3</t>
+  </si>
+  <si>
+    <t>Jennifer Kim + Shakthi Guruswami</t>
+  </si>
+  <si>
+    <t>Evan Chen + Veronica Chang</t>
+  </si>
+  <si>
+    <t>Geoffray Lee + Winnie Wu</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>WS2</t>
+  </si>
+  <si>
+    <t>Jamie Yip</t>
+  </si>
+  <si>
+    <t>Rachel Ye</t>
+  </si>
+  <si>
+    <t>Adam Dinh + Steffi Ling</t>
+  </si>
+  <si>
+    <t>Leah Diep + Emily Chen</t>
+  </si>
+  <si>
+    <t>WS3</t>
+  </si>
+  <si>
+    <t>Jenny Lei</t>
+  </si>
+  <si>
+    <t>Gaby imholte</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>Alexa Tyberg</t>
+  </si>
+  <si>
+    <t>Leyang Ding + Richard Huang</t>
+  </si>
+  <si>
+    <t>Jerry Qiu + Suhani</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>Donnovan Saelee + Gaby Imholte</t>
+  </si>
+  <si>
+    <t>MS1</t>
+  </si>
+  <si>
+    <t>Sam Lai</t>
+  </si>
+  <si>
+    <t>Nachiketh Karthik</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>Kyle Fang + Adrian Luo</t>
+  </si>
+  <si>
+    <t>Livia RIce</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>MS2</t>
+  </si>
+  <si>
+    <t>Harry Liu</t>
+  </si>
+  <si>
+    <t>Max Xing</t>
+  </si>
+  <si>
+    <t>Leyang Ding</t>
+  </si>
+  <si>
+    <t>MS3</t>
+  </si>
+  <si>
+    <t>Justin Chen</t>
+  </si>
+  <si>
+    <t>Luke Shen</t>
+  </si>
+  <si>
+    <t>MS4</t>
+  </si>
+  <si>
+    <t>Jon Moser</t>
+  </si>
+  <si>
+    <t>Melvin Keat</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>Mariano Elizondo</t>
+  </si>
+  <si>
+    <t>Jason Chen</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>MD7</t>
+  </si>
+  <si>
+    <t>Samarth + Yawei</t>
+  </si>
+  <si>
+    <t>Hao Yuan Zhu + Yuxin Yang</t>
+  </si>
+  <si>
+    <t>MD9</t>
+  </si>
+  <si>
+    <t>Aaron Lim + Aaron Kwan</t>
+  </si>
+  <si>
+    <t>Fahao Mei + Howell Zhang</t>
+  </si>
+  <si>
+    <t>Geoffray Lee</t>
+  </si>
+  <si>
+    <t>MD12</t>
+  </si>
+  <si>
+    <t>Josh Luo + Karthik Villavan</t>
+  </si>
+  <si>
+    <t>Michael Spencer + Kleber Diaz</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>MD8</t>
+  </si>
+  <si>
+    <t>Kyle Kimura + michael salim</t>
+  </si>
+  <si>
+    <t>MD11</t>
+  </si>
+  <si>
+    <t>Junru Su + Garrick Chan</t>
+  </si>
+  <si>
+    <t>Shakthi Guruswami + Nathan Thai</t>
+  </si>
+  <si>
+    <t>MS5</t>
+  </si>
+  <si>
+    <t>Sidney Wang</t>
+  </si>
+  <si>
+    <t>Sashreek Rewatkar</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>MD13</t>
+  </si>
+  <si>
+    <t>Jordan Kwong + Chinmay Nallapothula</t>
+  </si>
+  <si>
+    <t>MS6</t>
+  </si>
+  <si>
+    <t>Adrian Luo</t>
+  </si>
+  <si>
+    <t>Akshay Ganapathi</t>
+  </si>
+  <si>
+    <t>MD6</t>
+  </si>
+  <si>
+    <t>Sean Tan + Bill Wong</t>
+  </si>
+  <si>
+    <t>Justin Louie + Zenith Ma</t>
   </si>
   <si>
     <t>MD10</t>
   </si>
   <si>
-    <t>UCSC</t>
-  </si>
-  <si>
-    <t>Shakthi Guruswami + Rithwik Vaidun</t>
-  </si>
-  <si>
-    <t>Bryan Tang + Travis Choi</t>
-  </si>
-  <si>
-    <t>XD3</t>
-  </si>
-  <si>
-    <t>George Wu + Penny Liu</t>
-  </si>
-  <si>
-    <t>Benjamin Do + Niketana Thimma</t>
-  </si>
-  <si>
-    <t>XD4</t>
-  </si>
-  <si>
-    <t>Sashreek Rewatkar + Ishika Gwalherkar</t>
-  </si>
-  <si>
-    <t>Kevin Cuan + Iris Lee</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>WD2</t>
-  </si>
-  <si>
-    <t>Erin Chang + Ishika Gwalherkar</t>
-  </si>
-  <si>
-    <t>WD3</t>
-  </si>
-  <si>
-    <t>Benjamin Do + Juan David Liang</t>
-  </si>
-  <si>
-    <t>XD1</t>
-  </si>
-  <si>
-    <t>Akhilesh Nidamanuri + Emily Lam</t>
-  </si>
-  <si>
-    <t>Toan Le + Rupashi Bahl</t>
-  </si>
-  <si>
-    <t>Jenny Lei + Sydney Stachovic</t>
-  </si>
-  <si>
-    <t>XD9</t>
-  </si>
-  <si>
-    <t>Rithwik Vaidun + Rhea Rajan</t>
-  </si>
-  <si>
-    <t>Kenneth Darla + Shani Chiu</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>Erika Lai + Iris Lee</t>
-  </si>
-  <si>
-    <t>XD6</t>
-  </si>
-  <si>
-    <t>Justin Larson + Livia Rice</t>
-  </si>
-  <si>
-    <t>Khoa Nguyen + Natalie Luong</t>
-  </si>
-  <si>
-    <t>Leyang Ding + Xin Huang</t>
-  </si>
-  <si>
-    <t>Benson Ngai + Rithika Oumapathy</t>
-  </si>
-  <si>
-    <t>Emily Kung + Alex Nguyen</t>
-  </si>
-  <si>
-    <t>WD6</t>
-  </si>
-  <si>
-    <t>Rhea Rajan + Jenna Nguyen</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>XD5</t>
-  </si>
-  <si>
-    <t>Adam Dinh + Minh Nguyen</t>
-  </si>
-  <si>
-    <t>Seong Kang Kwong + Sankhya Gunda</t>
-  </si>
-  <si>
-    <t>Yuxin Yang + Jenny Lei</t>
-  </si>
-  <si>
-    <t>Emily Lam + Jennifer Kim</t>
-  </si>
-  <si>
-    <t>Niketana Thimma + Genevieve Le</t>
-  </si>
-  <si>
-    <t>Vivian Wang + Jolene Wei</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>WD5</t>
-  </si>
-  <si>
-    <t>Sandara Cabagbag + Chelsea Lin</t>
-  </si>
-  <si>
-    <t>Jiaying Zhang + Yi Zhong</t>
-  </si>
-  <si>
-    <t>MD12</t>
-  </si>
-  <si>
-    <t>WS1</t>
-  </si>
-  <si>
-    <t>Rithika Oumapathy</t>
-  </si>
-  <si>
-    <t>Rupashi Bahl</t>
-  </si>
-  <si>
-    <t>MD4</t>
-  </si>
-  <si>
-    <t>Adam Vu + Sashreek Rewatkar</t>
-  </si>
-  <si>
-    <t>Justin Larson + Sam Sridhara</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>WS4</t>
-  </si>
-  <si>
-    <t>Jasmeet Dhillon</t>
-  </si>
-  <si>
-    <t>Sankhya Gunda</t>
-  </si>
-  <si>
-    <t>WS2</t>
-  </si>
-  <si>
-    <t>Ishika Gwalherkar</t>
-  </si>
-  <si>
-    <t>XD2</t>
-  </si>
-  <si>
-    <t>Richard Huang + Erika Lai</t>
-  </si>
-  <si>
-    <t>Chelsea Lin + Benny Wen</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>Adam Vu + Jennifer Kim</t>
-  </si>
-  <si>
-    <t>Erika Lai</t>
-  </si>
-  <si>
-    <t>WS5</t>
-  </si>
-  <si>
-    <t>Maina Berteloot</t>
-  </si>
-  <si>
-    <t>Natalie Luong</t>
-  </si>
-  <si>
-    <t>WS6</t>
-  </si>
-  <si>
-    <t>Amber Li</t>
-  </si>
-  <si>
-    <t>XD8</t>
-  </si>
-  <si>
-    <t>Shakthi Guruswami + Sydney Stachovic</t>
-  </si>
-  <si>
-    <t>Sandara Cabagbag + Isaac Li</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>WS3</t>
-  </si>
-  <si>
-    <t>Donnovan Saelee + Chonticha Phanphanit</t>
-  </si>
-  <si>
-    <t>MS5</t>
-  </si>
-  <si>
-    <t>Adrian Luu</t>
-  </si>
-  <si>
-    <t>Benjamin Do</t>
-  </si>
-  <si>
-    <t>Alex Nguyen + Alex Luong</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>Jenny Lei</t>
-  </si>
-  <si>
-    <t>XD7</t>
-  </si>
-  <si>
-    <t>Harry Liu + Jenna Nguyen</t>
-  </si>
-  <si>
-    <t>Giang Phi + Maina Berteloot</t>
-  </si>
-  <si>
-    <t>Akshay Ganapathi + Erin Chang</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>Jiaying Zhang</t>
-  </si>
-  <si>
-    <t>Jasmin Chan + Fiona Chen</t>
-  </si>
-  <si>
-    <t>Penny Liu</t>
-  </si>
-  <si>
-    <t>MD1</t>
-  </si>
-  <si>
-    <t>Richard Huang + Benson Ngai</t>
-  </si>
-  <si>
-    <t>Khang Nguyen + Tyler Yeh</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>Jenna Nguyen</t>
-  </si>
-  <si>
-    <t>MD2</t>
-  </si>
-  <si>
-    <t>Akhilesh Nidamanuri + Maharshi Mandapati</t>
-  </si>
-  <si>
-    <t>Sean Hsieh + Benny Wen</t>
-  </si>
-  <si>
-    <t>MD3</t>
-  </si>
-  <si>
-    <t>Jayden Ma + George Wu</t>
-  </si>
-  <si>
-    <t>Toan Le + Kyle Wong</t>
-  </si>
-  <si>
-    <t>MD11</t>
-  </si>
-  <si>
-    <t>Kyle Kimura + Adrian Luu</t>
-  </si>
-  <si>
-    <t>Ethan Phan + Kenneth Darla</t>
-  </si>
-  <si>
-    <t>Michael Salim + Nathan Pham</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>Genevieve Le + Tyler Yeh</t>
-  </si>
-  <si>
-    <t>Marc Ethan Saguiped + Carolyn</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>Hardy Chen</t>
-  </si>
-  <si>
-    <t>Yi Zhong</t>
-  </si>
-  <si>
-    <t>Sidney Wang + Jon Moser</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>MD6</t>
-  </si>
-  <si>
-    <t>Ran Chen + Justin Louie</t>
-  </si>
-  <si>
-    <t>Seong Kang Kwong + Logan Lei Chong</t>
-  </si>
-  <si>
-    <t>Sam Lai + Suneet Katrekar</t>
-  </si>
-  <si>
-    <t>Krishna Gupta + Kevin Cuan</t>
-  </si>
-  <si>
-    <t>MD8</t>
-  </si>
-  <si>
-    <t>Donnovan Saelee + Marc Ethan Saguiped</t>
-  </si>
-  <si>
-    <t>Paul Bishop + Parth Gopakumar</t>
-  </si>
-  <si>
-    <t>02:45</t>
-  </si>
-  <si>
-    <t>WS7</t>
-  </si>
-  <si>
-    <t>Jolene Wei</t>
-  </si>
-  <si>
-    <t>Sandara Cabagbag</t>
-  </si>
-  <si>
-    <t>Victor Shi + Curtis Luu</t>
-  </si>
-  <si>
-    <t>MS2</t>
-  </si>
-  <si>
-    <t>Sashreek Rewatkar</t>
-  </si>
-  <si>
-    <t>Kyle Wong</t>
-  </si>
-  <si>
-    <t>MS3</t>
-  </si>
-  <si>
-    <t>Akshay Ganapathi</t>
-  </si>
-  <si>
-    <t>Toan Le</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>Chonticha Phanphanit</t>
-  </si>
-  <si>
-    <t>MS6</t>
-  </si>
-  <si>
-    <t>Bryan Tang</t>
-  </si>
-  <si>
-    <t>Alex Luong</t>
+    <t>Ryan Lei + Taewan Yun</t>
+  </si>
+  <si>
+    <t>Jivan Krisna + Stanley Hu</t>
+  </si>
+  <si>
+    <t>MD14</t>
+  </si>
+  <si>
+    <t>Marc Ethan Saguiped + Nolan Cloud</t>
+  </si>
+  <si>
+    <t>MS9</t>
+  </si>
+  <si>
+    <t>Justin Larson</t>
+  </si>
+  <si>
+    <t>Fahao Mei</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>MS10</t>
+  </si>
+  <si>
+    <t>Bill Wong</t>
+  </si>
+  <si>
+    <t>Michael Spencer</t>
+  </si>
+  <si>
+    <t>MS11</t>
+  </si>
+  <si>
+    <t>Aaron Lim</t>
+  </si>
+  <si>
+    <t>Yuxin Yang</t>
+  </si>
+  <si>
+    <t>MS14</t>
+  </si>
+  <si>
+    <t>Aaron Kwan</t>
+  </si>
+  <si>
+    <t>Kleber Diaz</t>
   </si>
   <si>
     <t>MS7</t>
   </si>
   <si>
+    <t>Yawei</t>
+  </si>
+  <si>
     <t>Justin Louie</t>
   </si>
   <si>
-    <t>Travis Choi</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>Khang Nguyen</t>
-  </si>
-  <si>
-    <t>MS9</t>
-  </si>
-  <si>
-    <t>Ran Chen</t>
-  </si>
-  <si>
-    <t>MS10</t>
-  </si>
-  <si>
-    <t>Nicholas Cen</t>
-  </si>
-  <si>
-    <t>MD13</t>
-  </si>
-  <si>
-    <t>Jon Moser</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>Logan Lei Chong</t>
-  </si>
-  <si>
-    <t>Paul Bishop</t>
-  </si>
-  <si>
-    <t>MD5</t>
-  </si>
-  <si>
-    <t>Yuxin Yang + Hardy Chen</t>
-  </si>
-  <si>
-    <t>Garrick Chan + Junru Su</t>
-  </si>
-  <si>
-    <t>Donald Ly + Bill Wong</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>Victor Tran + Cheng Huan Yu</t>
-  </si>
-  <si>
-    <t>MD7</t>
-  </si>
-  <si>
-    <t>Nicholas Cen + Mervyn Neo</t>
-  </si>
-  <si>
-    <t>Khoa Tran + Khoa Nguyen</t>
-  </si>
-  <si>
-    <t>Stanley Hu + Shyam Sundararajan</t>
-  </si>
-  <si>
-    <t>Ryan Lei + Taewan Yun</t>
-  </si>
-  <si>
-    <t>MS1</t>
-  </si>
-  <si>
-    <t>Sam Lai</t>
-  </si>
-  <si>
-    <t>Leyang Ding</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>Geoffray Lee</t>
-  </si>
-  <si>
-    <t>MS4</t>
-  </si>
-  <si>
-    <t>Maharshi Mandapati</t>
-  </si>
-  <si>
-    <t>Sam Sridhara</t>
-  </si>
-  <si>
-    <t>Chenyi Zhang</t>
+    <t>MS12</t>
+  </si>
+  <si>
+    <t>Kyle Kimura</t>
+  </si>
+  <si>
+    <t>Stanley Hu</t>
+  </si>
+  <si>
+    <t>MS13</t>
+  </si>
+  <si>
+    <t>Michael Salim</t>
+  </si>
+  <si>
+    <t>Nathan Thai</t>
   </si>
   <si>
     <t>MS8</t>
   </si>
   <si>
-    <t>Harry Liu</t>
-  </si>
-  <si>
-    <t>Michael Salim</t>
-  </si>
-  <si>
-    <t>04:15</t>
-  </si>
-  <si>
-    <t>Sean Hsieh</t>
-  </si>
-  <si>
-    <t>MS11</t>
-  </si>
-  <si>
-    <t>Kai Wagner</t>
-  </si>
-  <si>
-    <t>Jordan Kwong + Chinmay Nallapothula</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>Aditya Nagpal</t>
-  </si>
-  <si>
-    <t>Kelvin Chong</t>
-  </si>
-  <si>
-    <t>04:45</t>
-  </si>
-  <si>
-    <t>Brandon Lee</t>
-  </si>
-  <si>
-    <t>MD9</t>
-  </si>
-  <si>
-    <t>Howell Zhang + Hao Yuan Zhu</t>
-  </si>
-  <si>
-    <t>Aaron Lim + Adrian Luo</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>Jun Quan Yap + Kien Than</t>
+    <t>Sean Tan</t>
+  </si>
+  <si>
+    <t>Jivan Krishna</t>
   </si>
   <si>
     <t>A-Team Tally</t>
@@ -1178,10 +1088,10 @@
         <v>15</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1197,7 +1107,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -1215,15 +1125,15 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$L$1)*$M$7:$M$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))+SUMPRODUCT(($H$7:$H$153=$L$1)*$N$7:$N$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$L$1)*$M$7:$M$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))+SUMPRODUCT(($H$7:$H$104=$L$1)*$N$7:$N$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="M3" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$M$1)*$M$7:$M$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))+SUMPRODUCT(($H$7:$H$153=$M$1)*$N$7:$N$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$M$1)*$M$7:$M$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))+SUMPRODUCT(($H$7:$H$104=$M$1)*$N$7:$N$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$N$1)*$M$7:$M$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))+SUMPRODUCT(($H$7:$H$153=$N$1)*$N$7:$N$153*((ISNUMBER(FIND("1",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$153,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$153,1))))&gt;0))</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$N$1)*$M$7:$M$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))+SUMPRODUCT(($H$7:$H$104=$N$1)*$N$7:$N$104*((ISNUMBER(FIND("1",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("2",RIGHT($D$7:$D$104,1)))+ISNUMBER(FIND("3",RIGHT($D$7:$D$104,1))))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
@@ -1240,7 +1150,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="3" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1258,15 +1168,15 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$L$1)*$M$7:$M$153)+SUMPRODUCT(($H$7:$H$153=$L$1)*$N$7:$N$153)</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$L$1)*$M$7:$M$104)+SUMPRODUCT(($H$7:$H$104=$L$1)*$N$7:$N$104)</f>
         <v>0</v>
       </c>
       <c r="M5" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$M$1)*$M$7:$M$153)+SUMPRODUCT(($H$7:$H$153=$M$1)*$N$7:$N$153)</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$M$1)*$M$7:$M$104)+SUMPRODUCT(($H$7:$H$104=$M$1)*$N$7:$N$104)</f>
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <f>SUMPRODUCT(($E$7:$E$153=$N$1)*$M$7:$M$153)+SUMPRODUCT(($H$7:$H$153=$N$1)*$N$7:$N$153)</f>
+        <f>SUMPRODUCT(($E$7:$E$104=$N$1)*$M$7:$M$104)+SUMPRODUCT(($H$7:$H$104=$N$1)*$N$7:$N$104)</f>
         <v>0</v>
       </c>
     </row>
@@ -1409,7 +1319,7 @@
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>27</v>
@@ -1458,14 +1368,14 @@
         <v>31</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>33</v>
@@ -1488,7 +1398,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>36</v>
@@ -1513,7 +1423,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>14</v>
@@ -1526,7 +1436,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="7"/>
@@ -1541,20 +1451,20 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="7"/>
@@ -1569,20 +1479,20 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="7"/>
@@ -1597,20 +1507,20 @@
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="7"/>
@@ -1625,20 +1535,20 @@
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="7"/>
@@ -1648,27 +1558,27 @@
     </row>
     <row r="19" spans="1:14" ht="20" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="6">
         <v>1</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="7"/>
@@ -1683,20 +1593,20 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="7"/>
@@ -1711,20 +1621,20 @@
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="7"/>
@@ -1739,20 +1649,20 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="7"/>
@@ -1767,20 +1677,20 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="7"/>
@@ -1795,20 +1705,20 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="7"/>
@@ -1818,27 +1728,27 @@
     </row>
     <row r="25" spans="1:14" ht="20" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B25" s="6">
         <v>1</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="7"/>
@@ -1853,20 +1763,20 @@
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="7"/>
@@ -1894,7 +1804,7 @@
         <v>15</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="7"/>
@@ -1909,20 +1819,20 @@
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="7"/>
@@ -1937,20 +1847,20 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="7"/>
@@ -1965,20 +1875,20 @@
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="7"/>
@@ -1988,27 +1898,27 @@
     </row>
     <row r="31" spans="1:14" ht="20" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B31" s="6">
         <v>1</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="7"/>
@@ -2023,20 +1933,20 @@
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="7"/>
@@ -2051,20 +1961,20 @@
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="7"/>
@@ -2079,20 +1989,20 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="7"/>
@@ -2107,20 +2017,20 @@
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="7"/>
@@ -2135,20 +2045,20 @@
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J36" s="6"/>
       <c r="K36" s="7"/>
@@ -2158,17 +2068,17 @@
     </row>
     <row r="37" spans="1:14" ht="20" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" s="6">
         <v>1</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>77</v>
@@ -2178,7 +2088,7 @@
         <v>15</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="7"/>
@@ -2193,20 +2103,20 @@
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J38" s="6"/>
       <c r="K38" s="7"/>
@@ -2221,20 +2131,20 @@
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" s="6"/>
       <c r="K39" s="7"/>
@@ -2249,20 +2159,20 @@
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J40" s="6"/>
       <c r="K40" s="7"/>
@@ -2277,20 +2187,20 @@
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="7"/>
@@ -2305,20 +2215,20 @@
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J42" s="6"/>
       <c r="K42" s="7"/>
@@ -2328,27 +2238,27 @@
     </row>
     <row r="43" spans="1:14" ht="20" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B43" s="6">
         <v>1</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="7"/>
@@ -2363,20 +2273,20 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J44" s="6"/>
       <c r="K44" s="7"/>
@@ -2391,20 +2301,20 @@
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="J45" s="6"/>
       <c r="K45" s="7"/>
@@ -2419,20 +2329,20 @@
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="J46" s="6"/>
       <c r="K46" s="7"/>
@@ -2447,20 +2357,20 @@
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47" s="7"/>
@@ -2475,20 +2385,20 @@
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="7"/>
@@ -2498,27 +2408,27 @@
     </row>
     <row r="49" spans="1:14" ht="20" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B49" s="6">
         <v>1</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J49" s="6"/>
       <c r="K49" s="7"/>
@@ -2533,20 +2443,20 @@
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="7"/>
@@ -2561,20 +2471,20 @@
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="7"/>
@@ -2589,20 +2499,20 @@
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="7"/>
@@ -2617,20 +2527,20 @@
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53" s="7"/>
@@ -2645,20 +2555,20 @@
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="J54" s="6"/>
       <c r="K54" s="7"/>
@@ -2668,27 +2578,27 @@
     </row>
     <row r="55" spans="1:14" ht="20" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B55" s="6">
         <v>1</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J55" s="6"/>
       <c r="K55" s="7"/>
@@ -2703,20 +2613,20 @@
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J56" s="6"/>
       <c r="K56" s="7"/>
@@ -2731,20 +2641,20 @@
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="J57" s="6"/>
       <c r="K57" s="7"/>
@@ -2759,20 +2669,20 @@
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="7"/>
@@ -2787,20 +2697,20 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="7"/>
@@ -2815,20 +2725,20 @@
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="J60" s="6"/>
       <c r="K60" s="7"/>
@@ -2838,27 +2748,27 @@
     </row>
     <row r="61" spans="1:14" ht="20" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B61" s="6">
         <v>1</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="7"/>
@@ -2873,20 +2783,20 @@
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J62" s="6"/>
       <c r="K62" s="7"/>
@@ -2901,20 +2811,20 @@
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="7"/>
@@ -2929,20 +2839,20 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64" s="7"/>
@@ -2957,20 +2867,20 @@
       </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="7"/>
@@ -2985,20 +2895,20 @@
       </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="7"/>
@@ -3008,27 +2918,27 @@
     </row>
     <row r="67" spans="1:14" ht="20" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B67" s="6">
         <v>1</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="7"/>
@@ -3043,20 +2953,20 @@
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="7"/>
@@ -3071,20 +2981,20 @@
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="7"/>
@@ -3099,20 +3009,20 @@
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="7"/>
@@ -3127,20 +3037,20 @@
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G71" s="6"/>
       <c r="H71" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="7"/>
@@ -3155,20 +3065,20 @@
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="G72" s="6"/>
       <c r="H72" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="7"/>
@@ -3178,27 +3088,27 @@
     </row>
     <row r="73" spans="1:14" ht="20" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B73" s="6">
         <v>1</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="G73" s="6"/>
       <c r="H73" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="7"/>
@@ -3213,20 +3123,20 @@
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="7"/>
@@ -3241,20 +3151,20 @@
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G75" s="6"/>
       <c r="H75" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="7"/>
@@ -3269,20 +3179,20 @@
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="7"/>
@@ -3297,20 +3207,20 @@
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="7"/>
@@ -3325,20 +3235,20 @@
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G78" s="6"/>
       <c r="H78" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="J78" s="6"/>
       <c r="K78" s="7"/>
@@ -3348,27 +3258,27 @@
     </row>
     <row r="79" spans="1:14" ht="20" customHeight="1">
       <c r="A79" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B79" s="6">
         <v>1</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G79" s="6"/>
       <c r="H79" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="J79" s="6"/>
       <c r="K79" s="7"/>
@@ -3383,17 +3293,17 @@
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G80" s="6"/>
       <c r="H80" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>128</v>
@@ -3411,20 +3321,20 @@
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G81" s="6"/>
       <c r="H81" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J81" s="6"/>
       <c r="K81" s="7"/>
@@ -3439,20 +3349,20 @@
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G82" s="6"/>
       <c r="H82" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82" s="7"/>
@@ -3467,20 +3377,20 @@
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="G83" s="6"/>
       <c r="H83" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J83" s="6"/>
       <c r="K83" s="7"/>
@@ -3495,20 +3405,20 @@
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G84" s="6"/>
       <c r="H84" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J84" s="6"/>
       <c r="K84" s="7"/>
@@ -3518,27 +3428,27 @@
     </row>
     <row r="85" spans="1:14" ht="20" customHeight="1">
       <c r="A85" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B85" s="6">
         <v>1</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85" s="7"/>
@@ -3553,20 +3463,20 @@
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J86" s="6"/>
       <c r="K86" s="7"/>
@@ -3581,20 +3491,20 @@
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G87" s="6"/>
       <c r="H87" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87" s="7"/>
@@ -3609,20 +3519,20 @@
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="J88" s="6"/>
       <c r="K88" s="7"/>
@@ -3637,20 +3547,20 @@
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G89" s="6"/>
       <c r="H89" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="J89" s="6"/>
       <c r="K89" s="7"/>
@@ -3665,20 +3575,20 @@
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J90" s="6"/>
       <c r="K90" s="7"/>
@@ -3688,27 +3598,27 @@
     </row>
     <row r="91" spans="1:14" ht="20" customHeight="1">
       <c r="A91" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B91" s="6">
         <v>1</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="G91" s="6"/>
       <c r="H91" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="J91" s="6"/>
       <c r="K91" s="7"/>
@@ -3723,20 +3633,20 @@
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G92" s="6"/>
       <c r="H92" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="J92" s="6"/>
       <c r="K92" s="7"/>
@@ -3751,20 +3661,20 @@
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G93" s="6"/>
       <c r="H93" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="J93" s="6"/>
       <c r="K93" s="7"/>
@@ -3779,20 +3689,20 @@
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="J94" s="6"/>
       <c r="K94" s="7"/>
@@ -3807,20 +3717,20 @@
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="J95" s="6"/>
       <c r="K95" s="7"/>
@@ -3835,20 +3745,20 @@
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G96" s="6"/>
       <c r="H96" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" s="6"/>
       <c r="K96" s="7"/>
@@ -3858,27 +3768,27 @@
     </row>
     <row r="97" spans="1:14" ht="20" customHeight="1">
       <c r="A97" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B97" s="6">
         <v>1</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G97" s="6"/>
       <c r="H97" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97" s="7"/>
@@ -3893,20 +3803,20 @@
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="G98" s="6"/>
       <c r="H98" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98" s="7"/>
@@ -3921,20 +3831,20 @@
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G99" s="6"/>
       <c r="H99" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J99" s="6"/>
       <c r="K99" s="7"/>
@@ -3949,20 +3859,20 @@
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="J100" s="6"/>
       <c r="K100" s="7"/>
@@ -3977,20 +3887,20 @@
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="7"/>
@@ -4005,20 +3915,20 @@
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="J102" s="6"/>
       <c r="K102" s="7"/>
@@ -4027,28 +3937,25 @@
       <c r="N102" s="6"/>
     </row>
     <row r="103" spans="1:14" ht="20" customHeight="1">
-      <c r="A103" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="B103" s="6">
         <v>1</v>
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="G103" s="6"/>
       <c r="H103" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103" s="7"/>
@@ -4056,1264 +3963,63 @@
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
     </row>
-    <row r="104" spans="1:14" ht="20" customHeight="1">
-      <c r="A104" s="5"/>
-      <c r="B104" s="6">
-        <v>2</v>
-      </c>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G104" s="6"/>
-      <c r="H104" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="J104" s="6"/>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="6"/>
-      <c r="N104" s="6"/>
-    </row>
-    <row r="105" spans="1:14" ht="20" customHeight="1">
-      <c r="A105" s="5"/>
-      <c r="B105" s="6">
-        <v>3</v>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G105" s="6"/>
-      <c r="H105" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="J105" s="6"/>
-      <c r="K105" s="7"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="6"/>
-      <c r="N105" s="6"/>
-    </row>
-    <row r="106" spans="1:14" ht="20" customHeight="1">
-      <c r="A106" s="5"/>
-      <c r="B106" s="6">
-        <v>4</v>
-      </c>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G106" s="6"/>
-      <c r="H106" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="J106" s="6"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="6"/>
-      <c r="N106" s="6"/>
-    </row>
-    <row r="107" spans="1:14" ht="20" customHeight="1">
-      <c r="A107" s="5"/>
-      <c r="B107" s="6">
-        <v>5</v>
-      </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G107" s="6"/>
-      <c r="H107" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="J107" s="6"/>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7"/>
-      <c r="M107" s="6"/>
-      <c r="N107" s="6"/>
-    </row>
-    <row r="108" spans="1:14" ht="20" customHeight="1">
-      <c r="A108" s="5"/>
-      <c r="B108" s="6">
-        <v>6</v>
-      </c>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G108" s="6"/>
-      <c r="H108" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J108" s="6"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="6"/>
-    </row>
-    <row r="109" spans="1:14" ht="20" customHeight="1">
-      <c r="A109" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B109" s="6">
-        <v>1</v>
-      </c>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G109" s="6"/>
-      <c r="H109" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="J109" s="6"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7"/>
-      <c r="M109" s="6"/>
-      <c r="N109" s="6"/>
-    </row>
-    <row r="110" spans="1:14" ht="20" customHeight="1">
-      <c r="A110" s="5"/>
-      <c r="B110" s="6">
-        <v>2</v>
-      </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G110" s="6"/>
-      <c r="H110" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="J110" s="6"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="6"/>
-      <c r="N110" s="6"/>
-    </row>
-    <row r="111" spans="1:14" ht="20" customHeight="1">
-      <c r="A111" s="5"/>
-      <c r="B111" s="6">
-        <v>3</v>
-      </c>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G111" s="6"/>
-      <c r="H111" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="J111" s="6"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="6"/>
-      <c r="N111" s="6"/>
-    </row>
-    <row r="112" spans="1:14" ht="20" customHeight="1">
-      <c r="A112" s="5"/>
-      <c r="B112" s="6">
-        <v>4</v>
-      </c>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G112" s="6"/>
-      <c r="H112" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="J112" s="6"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="6"/>
-      <c r="N112" s="6"/>
-    </row>
-    <row r="113" spans="1:14" ht="20" customHeight="1">
-      <c r="A113" s="5"/>
-      <c r="B113" s="6">
-        <v>5</v>
-      </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G113" s="6"/>
-      <c r="H113" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="J113" s="6"/>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="6"/>
-      <c r="N113" s="6"/>
-    </row>
-    <row r="114" spans="1:14" ht="20" customHeight="1">
-      <c r="A114" s="5"/>
-      <c r="B114" s="6">
-        <v>6</v>
-      </c>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G114" s="6"/>
-      <c r="H114" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J114" s="6"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="6"/>
-      <c r="N114" s="6"/>
-    </row>
-    <row r="115" spans="1:14" ht="20" customHeight="1">
-      <c r="A115" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B115" s="6">
-        <v>1</v>
-      </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G115" s="6"/>
-      <c r="H115" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J115" s="6"/>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="6"/>
-      <c r="N115" s="6"/>
-    </row>
-    <row r="116" spans="1:14" ht="20" customHeight="1">
-      <c r="A116" s="5"/>
-      <c r="B116" s="6">
-        <v>2</v>
-      </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G116" s="6"/>
-      <c r="H116" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J116" s="6"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="6"/>
-      <c r="N116" s="6"/>
-    </row>
-    <row r="117" spans="1:14" ht="20" customHeight="1">
-      <c r="A117" s="5"/>
-      <c r="B117" s="6">
-        <v>3</v>
-      </c>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G117" s="6"/>
-      <c r="H117" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="J117" s="6"/>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7"/>
-      <c r="M117" s="6"/>
-      <c r="N117" s="6"/>
-    </row>
-    <row r="118" spans="1:14" ht="20" customHeight="1">
-      <c r="A118" s="5"/>
-      <c r="B118" s="6">
-        <v>4</v>
-      </c>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="G118" s="6"/>
-      <c r="H118" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="J118" s="6"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="6"/>
-      <c r="N118" s="6"/>
-    </row>
-    <row r="119" spans="1:14" ht="20" customHeight="1">
-      <c r="A119" s="5"/>
-      <c r="B119" s="6">
-        <v>5</v>
-      </c>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G119" s="6"/>
-      <c r="H119" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="J119" s="6"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="6"/>
-      <c r="N119" s="6"/>
-    </row>
-    <row r="120" spans="1:14" ht="20" customHeight="1">
-      <c r="A120" s="5"/>
-      <c r="B120" s="6">
-        <v>6</v>
-      </c>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G120" s="6"/>
-      <c r="H120" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="J120" s="6"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="6"/>
-      <c r="N120" s="6"/>
-    </row>
-    <row r="121" spans="1:14" ht="20" customHeight="1">
-      <c r="A121" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B121" s="6">
-        <v>1</v>
-      </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G121" s="6"/>
-      <c r="H121" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="J121" s="6"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="6"/>
-      <c r="N121" s="6"/>
-    </row>
-    <row r="122" spans="1:14" ht="20" customHeight="1">
-      <c r="A122" s="5"/>
-      <c r="B122" s="6">
-        <v>2</v>
-      </c>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="G122" s="6"/>
-      <c r="H122" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I122" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="J122" s="6"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="6"/>
-      <c r="N122" s="6"/>
-    </row>
-    <row r="123" spans="1:14" ht="20" customHeight="1">
-      <c r="A123" s="5"/>
-      <c r="B123" s="6">
-        <v>3</v>
-      </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G123" s="6"/>
-      <c r="H123" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="J123" s="6"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="6"/>
-      <c r="N123" s="6"/>
-    </row>
-    <row r="124" spans="1:14" ht="20" customHeight="1">
-      <c r="A124" s="5"/>
-      <c r="B124" s="6">
-        <v>4</v>
-      </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G124" s="6"/>
-      <c r="H124" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="J124" s="6"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="6"/>
-      <c r="N124" s="6"/>
-    </row>
-    <row r="125" spans="1:14" ht="20" customHeight="1">
-      <c r="A125" s="5"/>
-      <c r="B125" s="6">
-        <v>5</v>
-      </c>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G125" s="6"/>
-      <c r="H125" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="J125" s="6"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="6"/>
-      <c r="N125" s="6"/>
-    </row>
-    <row r="126" spans="1:14" ht="20" customHeight="1">
-      <c r="A126" s="5"/>
-      <c r="B126" s="6">
-        <v>6</v>
-      </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="G126" s="6"/>
-      <c r="H126" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I126" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J126" s="6"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="6"/>
-      <c r="N126" s="6"/>
-    </row>
-    <row r="127" spans="1:14" ht="20" customHeight="1">
-      <c r="A127" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B127" s="6">
-        <v>1</v>
-      </c>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="G127" s="6"/>
-      <c r="H127" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="J127" s="6"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="6"/>
-      <c r="N127" s="6"/>
-    </row>
-    <row r="128" spans="1:14" ht="20" customHeight="1">
-      <c r="A128" s="5"/>
-      <c r="B128" s="6">
-        <v>2</v>
-      </c>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G128" s="6"/>
-      <c r="H128" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="J128" s="6"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="6"/>
-      <c r="N128" s="6"/>
-    </row>
-    <row r="129" spans="1:14" ht="20" customHeight="1">
-      <c r="A129" s="5"/>
-      <c r="B129" s="6">
-        <v>3</v>
-      </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="G129" s="6"/>
-      <c r="H129" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="J129" s="6"/>
-      <c r="K129" s="7"/>
-      <c r="L129" s="7"/>
-      <c r="M129" s="6"/>
-      <c r="N129" s="6"/>
-    </row>
-    <row r="130" spans="1:14" ht="20" customHeight="1">
-      <c r="A130" s="5"/>
-      <c r="B130" s="6">
-        <v>4</v>
-      </c>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G130" s="6"/>
-      <c r="H130" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="J130" s="6"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="6"/>
-      <c r="N130" s="6"/>
-    </row>
-    <row r="131" spans="1:14" ht="20" customHeight="1">
-      <c r="A131" s="5"/>
-      <c r="B131" s="6">
-        <v>5</v>
-      </c>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G131" s="6"/>
-      <c r="H131" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="J131" s="6"/>
-      <c r="K131" s="7"/>
-      <c r="L131" s="7"/>
-      <c r="M131" s="6"/>
-      <c r="N131" s="6"/>
-    </row>
-    <row r="132" spans="1:14" ht="20" customHeight="1">
-      <c r="A132" s="5"/>
-      <c r="B132" s="6">
-        <v>6</v>
-      </c>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G132" s="6"/>
-      <c r="H132" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="J132" s="6"/>
-      <c r="K132" s="7"/>
-      <c r="L132" s="7"/>
-      <c r="M132" s="6"/>
-      <c r="N132" s="6"/>
-    </row>
-    <row r="133" spans="1:14" ht="20" customHeight="1">
-      <c r="A133" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B133" s="6">
-        <v>1</v>
-      </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="G133" s="6"/>
-      <c r="H133" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I133" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="J133" s="6"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="6"/>
-      <c r="N133" s="6"/>
-    </row>
-    <row r="134" spans="1:14" ht="20" customHeight="1">
-      <c r="A134" s="5"/>
-      <c r="B134" s="6">
-        <v>2</v>
-      </c>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G134" s="6"/>
-      <c r="H134" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="J134" s="6"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="6"/>
-      <c r="N134" s="6"/>
-    </row>
-    <row r="135" spans="1:14" ht="20" customHeight="1">
-      <c r="A135" s="5"/>
-      <c r="B135" s="6">
-        <v>3</v>
-      </c>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E135" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G135" s="6"/>
-      <c r="H135" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J135" s="6"/>
-      <c r="K135" s="7"/>
-      <c r="L135" s="7"/>
-      <c r="M135" s="6"/>
-      <c r="N135" s="6"/>
-    </row>
-    <row r="136" spans="1:14" ht="20" customHeight="1">
-      <c r="A136" s="5"/>
-      <c r="B136" s="6">
-        <v>4</v>
-      </c>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="G136" s="6"/>
-      <c r="H136" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J136" s="6"/>
-      <c r="K136" s="7"/>
-      <c r="L136" s="7"/>
-      <c r="M136" s="6"/>
-      <c r="N136" s="6"/>
-    </row>
-    <row r="137" spans="1:14" ht="20" customHeight="1">
-      <c r="A137" s="5"/>
-      <c r="B137" s="6">
-        <v>5</v>
-      </c>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G137" s="6"/>
-      <c r="H137" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J137" s="6"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="6"/>
-      <c r="N137" s="6"/>
-    </row>
-    <row r="138" spans="1:14" ht="20" customHeight="1">
-      <c r="A138" s="5"/>
-      <c r="B138" s="6">
-        <v>6</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G138" s="6"/>
-      <c r="H138" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J138" s="6"/>
-      <c r="K138" s="7"/>
-      <c r="L138" s="7"/>
-      <c r="M138" s="6"/>
-      <c r="N138" s="6"/>
-    </row>
-    <row r="139" spans="1:14" ht="20" customHeight="1">
-      <c r="A139" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B139" s="6">
-        <v>1</v>
-      </c>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G139" s="6"/>
-      <c r="H139" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J139" s="6"/>
-      <c r="K139" s="7"/>
-      <c r="L139" s="7"/>
-      <c r="M139" s="6"/>
-      <c r="N139" s="6"/>
-    </row>
-    <row r="140" spans="1:14" ht="20" customHeight="1">
-      <c r="A140" s="5"/>
-      <c r="B140" s="6">
-        <v>2</v>
-      </c>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="E140" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G140" s="6"/>
-      <c r="H140" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="J140" s="6"/>
-      <c r="K140" s="7"/>
-      <c r="L140" s="7"/>
-      <c r="M140" s="6"/>
-      <c r="N140" s="6"/>
-    </row>
-    <row r="141" spans="1:14" ht="20" customHeight="1">
-      <c r="A141" s="5"/>
-      <c r="B141" s="6">
-        <v>3</v>
-      </c>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G141" s="6"/>
-      <c r="H141" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="J141" s="6"/>
-      <c r="K141" s="7"/>
-      <c r="L141" s="7"/>
-      <c r="M141" s="6"/>
-      <c r="N141" s="6"/>
-    </row>
-    <row r="142" spans="1:14" ht="20" customHeight="1">
-      <c r="A142" s="5"/>
-      <c r="B142" s="6">
-        <v>4</v>
-      </c>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G142" s="6"/>
-      <c r="H142" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="J142" s="6"/>
-      <c r="K142" s="7"/>
-      <c r="L142" s="7"/>
-      <c r="M142" s="6"/>
-      <c r="N142" s="6"/>
-    </row>
-    <row r="143" spans="1:14" ht="20" customHeight="1">
-      <c r="A143" s="5"/>
-      <c r="B143" s="6">
-        <v>5</v>
-      </c>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G143" s="6"/>
-      <c r="H143" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J143" s="6"/>
-      <c r="K143" s="7"/>
-      <c r="L143" s="7"/>
-      <c r="M143" s="6"/>
-      <c r="N143" s="6"/>
-    </row>
-    <row r="144" spans="1:14" ht="20" customHeight="1">
-      <c r="A144" s="5"/>
-      <c r="B144" s="6">
-        <v>6</v>
-      </c>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="G144" s="6"/>
-      <c r="H144" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="J144" s="6"/>
-      <c r="K144" s="7"/>
-      <c r="L144" s="7"/>
-      <c r="M144" s="6"/>
-      <c r="N144" s="6"/>
-    </row>
-    <row r="145" spans="1:14" ht="20" customHeight="1">
-      <c r="A145" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B145" s="6">
-        <v>1</v>
-      </c>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="E145" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G145" s="6"/>
-      <c r="H145" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="J145" s="6"/>
-      <c r="K145" s="7"/>
-      <c r="L145" s="7"/>
-      <c r="M145" s="6"/>
-      <c r="N145" s="6"/>
-    </row>
-    <row r="146" spans="1:14" ht="20" customHeight="1">
-      <c r="A146" s="5"/>
-      <c r="B146" s="6">
-        <v>2</v>
-      </c>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E146" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G146" s="6"/>
-      <c r="H146" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J146" s="6"/>
-      <c r="K146" s="7"/>
-      <c r="L146" s="7"/>
-      <c r="M146" s="6"/>
-      <c r="N146" s="6"/>
-    </row>
-    <row r="147" spans="1:14" ht="20" customHeight="1">
-      <c r="B147" s="6">
-        <v>1</v>
-      </c>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G147" s="6"/>
-      <c r="H147" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I147" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J147" s="6"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="6"/>
-      <c r="N147" s="6"/>
-    </row>
-    <row r="148" spans="1:14" ht="20" customHeight="1"/>
-    <row r="149" spans="1:14" ht="20" customHeight="1"/>
-    <row r="150" spans="1:14" ht="20" customHeight="1"/>
-    <row r="151" spans="1:14" ht="20" customHeight="1"/>
-    <row r="152" spans="1:14" ht="20" customHeight="1"/>
-    <row r="153" spans="1:14" ht="20" customHeight="1"/>
-    <row r="154" spans="1:14" ht="20" customHeight="1"/>
-    <row r="155" spans="1:14" ht="20" customHeight="1"/>
-    <row r="156" spans="1:14" ht="20" customHeight="1"/>
-    <row r="157" spans="1:14" ht="20" customHeight="1"/>
-    <row r="158" spans="1:14" ht="20" customHeight="1"/>
-    <row r="159" spans="1:14" ht="20" customHeight="1"/>
-    <row r="160" spans="1:14" ht="20" customHeight="1"/>
+    <row r="104" spans="1:14" ht="20" customHeight="1"/>
+    <row r="105" spans="1:14" ht="20" customHeight="1"/>
+    <row r="106" spans="1:14" ht="20" customHeight="1"/>
+    <row r="107" spans="1:14" ht="20" customHeight="1"/>
+    <row r="108" spans="1:14" ht="20" customHeight="1"/>
+    <row r="109" spans="1:14" ht="20" customHeight="1"/>
+    <row r="110" spans="1:14" ht="20" customHeight="1"/>
+    <row r="111" spans="1:14" ht="20" customHeight="1"/>
+    <row r="112" spans="1:14" ht="20" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1"/>
+    <row r="114" ht="20" customHeight="1"/>
+    <row r="115" ht="20" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1"/>
+    <row r="119" ht="20" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1"/>
+    <row r="122" ht="20" customHeight="1"/>
+    <row r="123" ht="20" customHeight="1"/>
+    <row r="124" ht="20" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1"/>
+    <row r="126" ht="20" customHeight="1"/>
+    <row r="127" ht="20" customHeight="1"/>
+    <row r="128" ht="20" customHeight="1"/>
+    <row r="129" ht="20" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1"/>
+    <row r="132" ht="20" customHeight="1"/>
+    <row r="133" ht="20" customHeight="1"/>
+    <row r="134" ht="20" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1"/>
+    <row r="136" ht="20" customHeight="1"/>
+    <row r="137" ht="20" customHeight="1"/>
+    <row r="138" ht="20" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1"/>
+    <row r="140" ht="20" customHeight="1"/>
+    <row r="141" ht="20" customHeight="1"/>
+    <row r="142" ht="20" customHeight="1"/>
+    <row r="143" ht="20" customHeight="1"/>
+    <row r="144" ht="20" customHeight="1"/>
+    <row r="145" ht="20" customHeight="1"/>
+    <row r="146" ht="20" customHeight="1"/>
+    <row r="147" ht="20" customHeight="1"/>
+    <row r="148" ht="20" customHeight="1"/>
+    <row r="149" ht="20" customHeight="1"/>
+    <row r="150" ht="20" customHeight="1"/>
+    <row r="151" ht="20" customHeight="1"/>
+    <row r="152" ht="20" customHeight="1"/>
+    <row r="153" ht="20" customHeight="1"/>
+    <row r="154" ht="20" customHeight="1"/>
+    <row r="155" ht="20" customHeight="1"/>
+    <row r="156" ht="20" customHeight="1"/>
+    <row r="157" ht="20" customHeight="1"/>
+    <row r="158" ht="20" customHeight="1"/>
+    <row r="159" ht="20" customHeight="1"/>
+    <row r="160" ht="20" customHeight="1"/>
     <row r="161" ht="20" customHeight="1"/>
     <row r="162" ht="20" customHeight="1"/>
     <row r="163" ht="20" customHeight="1"/>
@@ -5356,7 +4062,7 @@
     <row r="200" ht="20" customHeight="1"/>
     <row r="201" ht="20" customHeight="1"/>
   </sheetData>
-  <mergeCells count="455">
+  <mergeCells count="315">
     <mergeCell ref="D1:K5"/>
     <mergeCell ref="A1:C5"/>
     <mergeCell ref="F6:G6"/>
@@ -5667,149 +4373,9 @@
     <mergeCell ref="F102:G102"/>
     <mergeCell ref="I102:J102"/>
     <mergeCell ref="K102:L102"/>
-    <mergeCell ref="A103:A108"/>
     <mergeCell ref="F103:G103"/>
     <mergeCell ref="I103:J103"/>
     <mergeCell ref="K103:L103"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="I104:J104"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="I106:J106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="A109:A114"/>
-    <mergeCell ref="F109:G109"/>
-    <mergeCell ref="I109:J109"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="F110:G110"/>
-    <mergeCell ref="I110:J110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="I114:J114"/>
-    <mergeCell ref="K114:L114"/>
-    <mergeCell ref="A115:A120"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="I115:J115"/>
-    <mergeCell ref="K115:L115"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="I117:J117"/>
-    <mergeCell ref="K117:L117"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="I118:J118"/>
-    <mergeCell ref="K118:L118"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="I119:J119"/>
-    <mergeCell ref="K119:L119"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="I120:J120"/>
-    <mergeCell ref="K120:L120"/>
-    <mergeCell ref="A121:A126"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="I121:J121"/>
-    <mergeCell ref="K121:L121"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="I123:J123"/>
-    <mergeCell ref="K123:L123"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="I124:J124"/>
-    <mergeCell ref="K124:L124"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="I125:J125"/>
-    <mergeCell ref="K125:L125"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="K126:L126"/>
-    <mergeCell ref="A127:A132"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="K128:L128"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="I129:J129"/>
-    <mergeCell ref="K129:L129"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="I130:J130"/>
-    <mergeCell ref="K130:L130"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="A133:A138"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="F134:G134"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="K137:L137"/>
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="A139:A144"/>
-    <mergeCell ref="F139:G139"/>
-    <mergeCell ref="I139:J139"/>
-    <mergeCell ref="K139:L139"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="I140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="I141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="I142:J142"/>
-    <mergeCell ref="K142:L142"/>
-    <mergeCell ref="F143:G143"/>
-    <mergeCell ref="I143:J143"/>
-    <mergeCell ref="K143:L143"/>
-    <mergeCell ref="F144:G144"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="F145:G145"/>
-    <mergeCell ref="I145:J145"/>
-    <mergeCell ref="K145:L145"/>
-    <mergeCell ref="F146:G146"/>
-    <mergeCell ref="I146:J146"/>
-    <mergeCell ref="K146:L146"/>
-    <mergeCell ref="F147:G147"/>
-    <mergeCell ref="I147:J147"/>
-    <mergeCell ref="K147:L147"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="L4:N4"/>
   </mergeCells>
